--- a/artfynd/A 4945-2025 artfynd.xlsx
+++ b/artfynd/A 4945-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1608,6 +1608,1026 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128484883</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91814</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bustadbäcken, Bustadbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>405352</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7024086</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128484439</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91360</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bustadbäcken, Bustadbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>405556</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7024299</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Örtrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128484597</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79191</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bustadbäcken, Bustadbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>405453</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7024142</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Översilad, grovvuxen gransumpskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128484529</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80136</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bustadbäcken, Bustadbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>405543</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7024164</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Örtrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128484645</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bustadbäcken, Bustadbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>405401</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7024067</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Översilad, grovvuxen gransumpskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128484648</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80136</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bustadbäcken, Bustadbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>405401</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7024067</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Översilad, grovvuxen gransumpskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128485596</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90821</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bustadbäcken, Bustadbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>405616</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7024400</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128484451</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92312</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Granriska</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lactarius zonarioides</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kühner &amp; Romagn.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bustadbäcken, Bustadbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>405556</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7024299</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Örtrik grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128484611</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91378</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bustadbäcken, Bustadbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>405443</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7024129</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Översilad, grovvuxen gransumpskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128484686</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79191</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bustadbäcken, Bustadbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>405413</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7024030</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4945-2025 artfynd.xlsx
+++ b/artfynd/A 4945-2025 artfynd.xlsx
@@ -1613,7 +1613,7 @@
         <v>128484883</v>
       </c>
       <c r="B10" t="n">
-        <v>91814</v>
+        <v>91906</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128484439</v>
       </c>
       <c r="B11" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128484597</v>
       </c>
       <c r="B12" t="n">
-        <v>79191</v>
+        <v>79242</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>128484529</v>
       </c>
       <c r="B13" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128484645</v>
+        <v>128485596</v>
       </c>
       <c r="B14" t="n">
-        <v>80135</v>
+        <v>90913</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,21 +2029,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>3286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405401</v>
+        <v>405616</v>
       </c>
       <c r="R14" t="n">
-        <v>7024067</v>
+        <v>7024400</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Översilad, grovvuxen gransumpskog</t>
+          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2120,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128484648</v>
+        <v>128484645</v>
       </c>
       <c r="B15" t="n">
-        <v>80136</v>
+        <v>80188</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128485596</v>
+        <v>128484648</v>
       </c>
       <c r="B16" t="n">
-        <v>90821</v>
+        <v>80189</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,21 +2233,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3286</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>405616</v>
+        <v>405401</v>
       </c>
       <c r="R16" t="n">
-        <v>7024400</v>
+        <v>7024067</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
+          <t>Översilad, grovvuxen gransumpskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2327,7 +2327,7 @@
         <v>128484451</v>
       </c>
       <c r="B17" t="n">
-        <v>92312</v>
+        <v>92404</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>128484611</v>
       </c>
       <c r="B18" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>128484686</v>
       </c>
       <c r="B19" t="n">
-        <v>79191</v>
+        <v>79242</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 4945-2025 artfynd.xlsx
+++ b/artfynd/A 4945-2025 artfynd.xlsx
@@ -2120,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128484645</v>
+        <v>128484648</v>
       </c>
       <c r="B15" t="n">
-        <v>80188</v>
+        <v>80189</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128484648</v>
+        <v>128484645</v>
       </c>
       <c r="B16" t="n">
-        <v>80189</v>
+        <v>80188</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,21 +2233,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>

--- a/artfynd/A 4945-2025 artfynd.xlsx
+++ b/artfynd/A 4945-2025 artfynd.xlsx
@@ -1613,7 +1613,7 @@
         <v>128484883</v>
       </c>
       <c r="B10" t="n">
-        <v>91906</v>
+        <v>91912</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128484439</v>
       </c>
       <c r="B11" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128484597</v>
       </c>
       <c r="B12" t="n">
-        <v>79242</v>
+        <v>79246</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>128484529</v>
       </c>
       <c r="B13" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>128485596</v>
       </c>
       <c r="B14" t="n">
-        <v>90913</v>
+        <v>90919</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>128484648</v>
       </c>
       <c r="B15" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>128484645</v>
       </c>
       <c r="B16" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128484451</v>
       </c>
       <c r="B17" t="n">
-        <v>92404</v>
+        <v>92410</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>128484611</v>
       </c>
       <c r="B18" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>128484686</v>
       </c>
       <c r="B19" t="n">
-        <v>79242</v>
+        <v>79246</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 4945-2025 artfynd.xlsx
+++ b/artfynd/A 4945-2025 artfynd.xlsx
@@ -1613,7 +1613,7 @@
         <v>128484883</v>
       </c>
       <c r="B10" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128484439</v>
       </c>
       <c r="B11" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>128485596</v>
       </c>
       <c r="B14" t="n">
-        <v>90919</v>
+        <v>90925</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128484648</v>
+        <v>128484645</v>
       </c>
       <c r="B15" t="n">
-        <v>80193</v>
+        <v>80192</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128484645</v>
+        <v>128484648</v>
       </c>
       <c r="B16" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,21 +2233,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2327,7 +2327,7 @@
         <v>128484451</v>
       </c>
       <c r="B17" t="n">
-        <v>92410</v>
+        <v>92416</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>128484611</v>
       </c>
       <c r="B18" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4945-2025 artfynd.xlsx
+++ b/artfynd/A 4945-2025 artfynd.xlsx
@@ -2018,10 +2018,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128485596</v>
+        <v>128484648</v>
       </c>
       <c r="B14" t="n">
-        <v>90925</v>
+        <v>80193</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,21 +2029,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3286</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405616</v>
+        <v>405401</v>
       </c>
       <c r="R14" t="n">
-        <v>7024400</v>
+        <v>7024067</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
+          <t>Översilad, grovvuxen gransumpskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128484648</v>
+        <v>128485596</v>
       </c>
       <c r="B16" t="n">
-        <v>80193</v>
+        <v>90925</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,21 +2233,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>3286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>405401</v>
+        <v>405616</v>
       </c>
       <c r="R16" t="n">
-        <v>7024067</v>
+        <v>7024400</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Översilad, grovvuxen gransumpskog</t>
+          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 4945-2025 artfynd.xlsx
+++ b/artfynd/A 4945-2025 artfynd.xlsx
@@ -1613,7 +1613,7 @@
         <v>128484883</v>
       </c>
       <c r="B10" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128484439</v>
       </c>
       <c r="B11" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128484597</v>
       </c>
       <c r="B12" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>128484529</v>
       </c>
       <c r="B13" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128484648</v>
+        <v>128484645</v>
       </c>
       <c r="B14" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,21 +2029,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2120,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128484645</v>
+        <v>128484648</v>
       </c>
       <c r="B15" t="n">
-        <v>80192</v>
+        <v>80195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2225,7 +2225,7 @@
         <v>128485596</v>
       </c>
       <c r="B16" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128484451</v>
       </c>
       <c r="B17" t="n">
-        <v>92416</v>
+        <v>92418</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>128484611</v>
       </c>
       <c r="B18" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>128484686</v>
       </c>
       <c r="B19" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 4945-2025 artfynd.xlsx
+++ b/artfynd/A 4945-2025 artfynd.xlsx
@@ -2018,10 +2018,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128484645</v>
+        <v>128484648</v>
       </c>
       <c r="B14" t="n">
-        <v>80194</v>
+        <v>80195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,21 +2029,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2120,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128484648</v>
+        <v>128485596</v>
       </c>
       <c r="B15" t="n">
-        <v>80195</v>
+        <v>90927</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>3286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405401</v>
+        <v>405616</v>
       </c>
       <c r="R15" t="n">
-        <v>7024067</v>
+        <v>7024400</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Översilad, grovvuxen gransumpskog</t>
+          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128485596</v>
+        <v>128484645</v>
       </c>
       <c r="B16" t="n">
-        <v>90927</v>
+        <v>80194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,21 +2233,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3286</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>405616</v>
+        <v>405401</v>
       </c>
       <c r="R16" t="n">
-        <v>7024400</v>
+        <v>7024067</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
+          <t>Översilad, grovvuxen gransumpskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 4945-2025 artfynd.xlsx
+++ b/artfynd/A 4945-2025 artfynd.xlsx
@@ -1613,7 +1613,7 @@
         <v>128484883</v>
       </c>
       <c r="B10" t="n">
-        <v>91920</v>
+        <v>91921</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128484439</v>
       </c>
       <c r="B11" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2120,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128485596</v>
+        <v>128484645</v>
       </c>
       <c r="B15" t="n">
-        <v>90927</v>
+        <v>80194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3286</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405616</v>
+        <v>405401</v>
       </c>
       <c r="R15" t="n">
-        <v>7024400</v>
+        <v>7024067</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
+          <t>Översilad, grovvuxen gransumpskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128484645</v>
+        <v>128485596</v>
       </c>
       <c r="B16" t="n">
-        <v>80194</v>
+        <v>90928</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,21 +2233,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>3286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>405401</v>
+        <v>405616</v>
       </c>
       <c r="R16" t="n">
-        <v>7024067</v>
+        <v>7024400</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Översilad, grovvuxen gransumpskog</t>
+          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2327,7 +2327,7 @@
         <v>128484451</v>
       </c>
       <c r="B17" t="n">
-        <v>92418</v>
+        <v>92419</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>128484611</v>
       </c>
       <c r="B18" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4945-2025 artfynd.xlsx
+++ b/artfynd/A 4945-2025 artfynd.xlsx
@@ -1613,7 +1613,7 @@
         <v>128484883</v>
       </c>
       <c r="B10" t="n">
-        <v>91921</v>
+        <v>91948</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128484439</v>
       </c>
       <c r="B11" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128484597</v>
       </c>
       <c r="B12" t="n">
-        <v>79248</v>
+        <v>79275</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>128484529</v>
       </c>
       <c r="B13" t="n">
-        <v>80195</v>
+        <v>80222</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128484648</v>
+        <v>128485596</v>
       </c>
       <c r="B14" t="n">
-        <v>80195</v>
+        <v>90955</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,21 +2029,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>3286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405401</v>
+        <v>405616</v>
       </c>
       <c r="R14" t="n">
-        <v>7024067</v>
+        <v>7024400</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Översilad, grovvuxen gransumpskog</t>
+          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2120,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128484645</v>
+        <v>128484648</v>
       </c>
       <c r="B15" t="n">
-        <v>80194</v>
+        <v>80222</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128485596</v>
+        <v>128484645</v>
       </c>
       <c r="B16" t="n">
-        <v>90928</v>
+        <v>80221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,21 +2233,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3286</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>405616</v>
+        <v>405401</v>
       </c>
       <c r="R16" t="n">
-        <v>7024400</v>
+        <v>7024067</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
+          <t>Översilad, grovvuxen gransumpskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2327,7 +2327,7 @@
         <v>128484451</v>
       </c>
       <c r="B17" t="n">
-        <v>92419</v>
+        <v>92446</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>128484611</v>
       </c>
       <c r="B18" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>128484686</v>
       </c>
       <c r="B19" t="n">
-        <v>79248</v>
+        <v>79275</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 4945-2025 artfynd.xlsx
+++ b/artfynd/A 4945-2025 artfynd.xlsx
@@ -1613,7 +1613,7 @@
         <v>128484883</v>
       </c>
       <c r="B10" t="n">
-        <v>91948</v>
+        <v>91953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128484439</v>
       </c>
       <c r="B11" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128484597</v>
       </c>
       <c r="B12" t="n">
-        <v>79275</v>
+        <v>79279</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>128484529</v>
       </c>
       <c r="B13" t="n">
-        <v>80222</v>
+        <v>80226</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128485596</v>
+        <v>128484648</v>
       </c>
       <c r="B14" t="n">
-        <v>90955</v>
+        <v>80226</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,21 +2029,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3286</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405616</v>
+        <v>405401</v>
       </c>
       <c r="R14" t="n">
-        <v>7024400</v>
+        <v>7024067</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
+          <t>Översilad, grovvuxen gransumpskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2120,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128484648</v>
+        <v>128485596</v>
       </c>
       <c r="B15" t="n">
-        <v>80222</v>
+        <v>90960</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>3286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405401</v>
+        <v>405616</v>
       </c>
       <c r="R15" t="n">
-        <v>7024067</v>
+        <v>7024400</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Översilad, grovvuxen gransumpskog</t>
+          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2225,7 +2225,7 @@
         <v>128484645</v>
       </c>
       <c r="B16" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128484451</v>
       </c>
       <c r="B17" t="n">
-        <v>92446</v>
+        <v>92451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>128484611</v>
       </c>
       <c r="B18" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>128484686</v>
       </c>
       <c r="B19" t="n">
-        <v>79275</v>
+        <v>79279</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 4945-2025 artfynd.xlsx
+++ b/artfynd/A 4945-2025 artfynd.xlsx
@@ -1613,7 +1613,7 @@
         <v>128484883</v>
       </c>
       <c r="B10" t="n">
-        <v>91953</v>
+        <v>91958</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128484439</v>
       </c>
       <c r="B11" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>128485596</v>
       </c>
       <c r="B15" t="n">
-        <v>90960</v>
+        <v>90965</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128484451</v>
       </c>
       <c r="B17" t="n">
-        <v>92451</v>
+        <v>92456</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>128484611</v>
       </c>
       <c r="B18" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4945-2025 artfynd.xlsx
+++ b/artfynd/A 4945-2025 artfynd.xlsx
@@ -1613,7 +1613,7 @@
         <v>128484883</v>
       </c>
       <c r="B10" t="n">
-        <v>91958</v>
+        <v>91962</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128484439</v>
       </c>
       <c r="B11" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128484597</v>
       </c>
       <c r="B12" t="n">
-        <v>79279</v>
+        <v>79283</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>128484529</v>
       </c>
       <c r="B13" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128484648</v>
+        <v>128485596</v>
       </c>
       <c r="B14" t="n">
-        <v>80226</v>
+        <v>90969</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,21 +2029,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>3286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405401</v>
+        <v>405616</v>
       </c>
       <c r="R14" t="n">
-        <v>7024067</v>
+        <v>7024400</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Översilad, grovvuxen gransumpskog</t>
+          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2120,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128485596</v>
+        <v>128484648</v>
       </c>
       <c r="B15" t="n">
-        <v>90965</v>
+        <v>80230</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3286</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405616</v>
+        <v>405401</v>
       </c>
       <c r="R15" t="n">
-        <v>7024400</v>
+        <v>7024067</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
+          <t>Översilad, grovvuxen gransumpskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2225,7 +2225,7 @@
         <v>128484645</v>
       </c>
       <c r="B16" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128484451</v>
       </c>
       <c r="B17" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>128484611</v>
       </c>
       <c r="B18" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>128484686</v>
       </c>
       <c r="B19" t="n">
-        <v>79279</v>
+        <v>79283</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 4945-2025 artfynd.xlsx
+++ b/artfynd/A 4945-2025 artfynd.xlsx
@@ -2018,10 +2018,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128485596</v>
+        <v>128484648</v>
       </c>
       <c r="B14" t="n">
-        <v>90969</v>
+        <v>80230</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,21 +2029,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3286</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405616</v>
+        <v>405401</v>
       </c>
       <c r="R14" t="n">
-        <v>7024400</v>
+        <v>7024067</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
+          <t>Översilad, grovvuxen gransumpskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2120,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128484648</v>
+        <v>128485596</v>
       </c>
       <c r="B15" t="n">
-        <v>80230</v>
+        <v>90969</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>3286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405401</v>
+        <v>405616</v>
       </c>
       <c r="R15" t="n">
-        <v>7024067</v>
+        <v>7024400</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Översilad, grovvuxen gransumpskog</t>
+          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 4945-2025 artfynd.xlsx
+++ b/artfynd/A 4945-2025 artfynd.xlsx
@@ -2018,10 +2018,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128484648</v>
+        <v>128484645</v>
       </c>
       <c r="B14" t="n">
-        <v>80230</v>
+        <v>80229</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,21 +2029,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2120,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128485596</v>
+        <v>128484648</v>
       </c>
       <c r="B15" t="n">
-        <v>90969</v>
+        <v>80230</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3286</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405616</v>
+        <v>405401</v>
       </c>
       <c r="R15" t="n">
-        <v>7024400</v>
+        <v>7024067</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
+          <t>Översilad, grovvuxen gransumpskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128484645</v>
+        <v>128485596</v>
       </c>
       <c r="B16" t="n">
-        <v>80229</v>
+        <v>90969</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,21 +2233,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>3286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>405401</v>
+        <v>405616</v>
       </c>
       <c r="R16" t="n">
-        <v>7024067</v>
+        <v>7024400</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Översilad, grovvuxen gransumpskog</t>
+          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 4945-2025 artfynd.xlsx
+++ b/artfynd/A 4945-2025 artfynd.xlsx
@@ -1613,7 +1613,7 @@
         <v>128484883</v>
       </c>
       <c r="B10" t="n">
-        <v>91962</v>
+        <v>91967</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>128484439</v>
       </c>
       <c r="B11" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>128484597</v>
       </c>
       <c r="B12" t="n">
-        <v>79283</v>
+        <v>79188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>128484529</v>
       </c>
       <c r="B13" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128484645</v>
+        <v>128485596</v>
       </c>
       <c r="B14" t="n">
-        <v>80229</v>
+        <v>90974</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2029,21 +2029,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>3286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405401</v>
+        <v>405616</v>
       </c>
       <c r="R14" t="n">
-        <v>7024067</v>
+        <v>7024400</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Översilad, grovvuxen gransumpskog</t>
+          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2120,10 +2120,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128484648</v>
+        <v>128484645</v>
       </c>
       <c r="B15" t="n">
-        <v>80230</v>
+        <v>80134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,21 +2131,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2222,10 +2222,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128485596</v>
+        <v>128484648</v>
       </c>
       <c r="B16" t="n">
-        <v>90969</v>
+        <v>80135</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,21 +2233,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3286</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>405616</v>
+        <v>405401</v>
       </c>
       <c r="R16" t="n">
-        <v>7024400</v>
+        <v>7024067</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
+          <t>Översilad, grovvuxen gransumpskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2327,7 +2327,7 @@
         <v>128484451</v>
       </c>
       <c r="B17" t="n">
-        <v>92460</v>
+        <v>92465</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>128484611</v>
       </c>
       <c r="B18" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>128484686</v>
       </c>
       <c r="B19" t="n">
-        <v>79283</v>
+        <v>79188</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 4945-2025 artfynd.xlsx
+++ b/artfynd/A 4945-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72972464</v>
+        <v>128484439</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,36 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väfjället NO, Jmt</t>
+          <t>Bustadbäcken, Bustadbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>405225.5025532217</v>
+        <v>405556</v>
       </c>
       <c r="R2" t="n">
-        <v>7023928.904693926</v>
+        <v>7024299</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -747,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,34 +754,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Örtrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Johnsen</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Johnsen</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>72972985</v>
+        <v>128484883</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,36 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väfjället NO, Jmt</t>
+          <t>Bustadbäcken, Bustadbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>405456.8639757569</v>
+        <v>405352</v>
       </c>
       <c r="R3" t="n">
-        <v>7024066.811757067</v>
+        <v>7024086</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,71 +856,68 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Johnsen</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Johnsen</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>72972733</v>
+        <v>128484597</v>
       </c>
       <c r="B4" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Väfjället NO, Jmt</t>
+          <t>Bustadbäcken, Bustadbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>405369.1764639277</v>
+        <v>405453</v>
       </c>
       <c r="R4" t="n">
-        <v>7024099.959867897</v>
+        <v>7024142</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,27 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,72 +958,68 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Översilad, grovvuxen gransumpskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Andreas Johnsen</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Johnsen</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>72972410</v>
+        <v>128484686</v>
       </c>
       <c r="B5" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>1249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Väfjället NO, Jmt</t>
+          <t>Bustadbäcken, Bustadbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>405225.5025532217</v>
+        <v>405413</v>
       </c>
       <c r="R5" t="n">
-        <v>7023928.904693926</v>
+        <v>7024030</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,22 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-09-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,34 +1060,33 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Johnsen</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Johnsen</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91846296</v>
+        <v>72972464</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,37 +1094,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Väfjället NO, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405366.0678472884</v>
+        <v>405226</v>
       </c>
       <c r="R6" t="n">
-        <v>7024086.118192286</v>
+        <v>7023929</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,22 +1150,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,75 +1164,69 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Andreas Johnsen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91846286</v>
+        <v>72972733</v>
       </c>
       <c r="B7" t="n">
-        <v>95717</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220686</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Väfjället NO, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405368.79242956</v>
+        <v>405369</v>
       </c>
       <c r="R7" t="n">
-        <v>7024086.936774109</v>
+        <v>7024100</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,22 +1250,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,37 +1269,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Andreas Johnsen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>91846299</v>
+        <v>99108941</v>
       </c>
       <c r="B8" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,37 +1299,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Väfjället Ö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405370.0222961347</v>
+        <v>405372</v>
       </c>
       <c r="R8" t="n">
-        <v>7024082.855332156</v>
+        <v>7023949</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1443,27 +1356,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,37 +1375,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Andreas Johnsen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>99108965</v>
+        <v>99109084</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1537,13 +1432,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>405371.7123762253</v>
+        <v>405532</v>
       </c>
       <c r="R9" t="n">
-        <v>7024002.799881374</v>
+        <v>7024100</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,19 +1465,9 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,32 +1495,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128484883</v>
+        <v>128484529</v>
       </c>
       <c r="B10" t="n">
-        <v>91970</v>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1645,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>405352</v>
+        <v>405543</v>
       </c>
       <c r="R10" t="n">
-        <v>7024086</v>
+        <v>7024164</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1694,7 +1579,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
+          <t>Örtrik grannaturskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1712,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128484439</v>
+        <v>128484648</v>
       </c>
       <c r="B11" t="n">
-        <v>91515</v>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,21 +1608,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1747,10 +1632,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>405556</v>
+        <v>405401</v>
       </c>
       <c r="R11" t="n">
-        <v>7024299</v>
+        <v>7024067</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,7 +1681,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Örtrik grannaturskog</t>
+          <t>Översilad, grovvuxen gransumpskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1814,32 +1699,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128484597</v>
+        <v>128485596</v>
       </c>
       <c r="B12" t="n">
-        <v>79188</v>
+        <v>91361</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1249</v>
+        <v>3286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1849,10 +1734,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405453</v>
+        <v>405616</v>
       </c>
       <c r="R12" t="n">
-        <v>7024142</v>
+        <v>7024400</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1898,7 +1783,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Översilad, grovvuxen gransumpskog</t>
+          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1916,32 +1801,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128484529</v>
+        <v>128484451</v>
       </c>
       <c r="B13" t="n">
-        <v>80135</v>
+        <v>92886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>4787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,10 +1836,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405543</v>
+        <v>405556</v>
       </c>
       <c r="R13" t="n">
-        <v>7024164</v>
+        <v>7024299</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,45 +1903,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128485596</v>
+        <v>99108965</v>
       </c>
       <c r="B14" t="n">
-        <v>90976</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3286</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bustadbäcken, Bustadbäcken, Jmt</t>
+          <t>Väfjället Ö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405616</v>
+        <v>405372</v>
       </c>
       <c r="R14" t="n">
-        <v>7024400</v>
+        <v>7024003</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2083,12 +1971,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2097,33 +1985,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Andreas Johnsen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Andreas Johnsen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128484648</v>
+        <v>72972985</v>
       </c>
       <c r="B15" t="n">
-        <v>80135</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2131,31 +2015,33 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bustadbäcken, Bustadbäcken, Jmt</t>
+          <t>Väfjället NO, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405401</v>
+        <v>405457</v>
       </c>
       <c r="R15" t="n">
         <v>7024067</v>
@@ -2185,12 +2071,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2018-09-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2018-09-01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,23 +2085,19 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Översilad, grovvuxen gransumpskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Andreas Johnsen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Andreas Johnsen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2225,7 +2107,7 @@
         <v>128484645</v>
       </c>
       <c r="B16" t="n">
-        <v>80134</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,10 +2206,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128484451</v>
+        <v>72972410</v>
       </c>
       <c r="B17" t="n">
-        <v>92468</v>
+        <v>80460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,34 +2217,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4787</v>
+        <v>6461</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bustadbäcken, Bustadbäcken, Jmt</t>
+          <t>Väfjället NO, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>405556</v>
+        <v>405226</v>
       </c>
       <c r="R17" t="n">
-        <v>7024299</v>
+        <v>7023929</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,12 +2274,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2018-09-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2018-09-01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2403,71 +2288,67 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Örtrik grannaturskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Andreas Johnsen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Andreas Johnsen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128484611</v>
+        <v>91846299</v>
       </c>
       <c r="B18" t="n">
-        <v>91533</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bustadbäcken, Bustadbäcken, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405443</v>
+        <v>405370</v>
       </c>
       <c r="R18" t="n">
-        <v>7024129</v>
+        <v>7024083</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2491,12 +2372,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2019-10-31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2507,69 +2393,68 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Översilad, grovvuxen gransumpskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128484686</v>
+        <v>91846296</v>
       </c>
       <c r="B19" t="n">
-        <v>79188</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1249</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bustadbäcken, Bustadbäcken, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>405413</v>
+        <v>405366</v>
       </c>
       <c r="R19" t="n">
-        <v>7024030</v>
+        <v>7024086</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2593,12 +2478,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2019-10-31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2609,24 +2494,225 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>91846294</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Jämtlands län, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>405338</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7023933</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2019-10-31</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>91846286</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Jämtlands län, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>405369</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7024087</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2019-10-31</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4945-2025 artfynd.xlsx
+++ b/artfynd/A 4945-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128484439</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128484883</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128484597</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128484686</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72972464</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1285,6 +1315,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72972733</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99108941</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1492,6 +1532,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99109084</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1594,6 +1639,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128484529</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1696,6 +1746,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128484648</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1798,6 +1853,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128485596</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1900,6 +1960,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128484451</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2001,6 +2066,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99108965</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2101,6 +2171,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72972985</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2203,6 +2278,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128484645</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72972410</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2410,6 +2495,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91846299</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2511,6 +2601,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91846296</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2612,6 +2707,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91846294</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2713,8 +2813,35 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91846286</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>